--- a/education_forms/050_english_pronunciation_quiz--education_forms.xlsx
+++ b/education_forms/050_english_pronunciation_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_answer1</t>
+          <t>question1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>user_answer</t>
+          <t>Correct Pronunciation of "hello"</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>audio_file1</t>
+          <t>question2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>audio_file</t>
+          <t>Correct Pronunciation of "cat"</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>correct_answer1</t>
+          <t>question3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>Pronunciation of "dog"</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_answer2</t>
+          <t>question4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>user_answer</t>
+          <t>Correct Pronunciation of "mouse"</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>correct_answer2</t>
+          <t>question5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>correct_answer</t>
+          <t>Pronunciation of "apple"</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>audio_file2</t>
+          <t>question6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>audio_file</t>
+          <t>Pronunciation of "bank"</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>question7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>Pronunciation of "phone"</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,21 +676,113 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quiz_type</t>
+          <t>question8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>quiz_type</t>
+          <t>How often do you practice English pronunciation?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>question9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>When do you usually practice English pronunciation?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>question10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Are you a native English speaker?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>question11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Which languages do you speak fluently besides English?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>question12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Additional languages you speak fluently</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,34 +827,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quiz_type_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>audio</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quiz_type_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>question4_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>question4_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>question6_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>question6_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>question11_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>question11_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>question11_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
